--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="153">
   <si>
     <t>2.1</t>
   </si>
@@ -410,6 +410,69 @@
   </si>
   <si>
     <t>всегда можно взять контейнер и наполнять его сколь угодно долго классами (анонимными объектами), содержащими разные параметры и контейнеры с нужными значениями</t>
+  </si>
+  <si>
+    <t>102 91</t>
+  </si>
+  <si>
+    <t>81 17</t>
+  </si>
+  <si>
+    <t>82 101</t>
+  </si>
+  <si>
+    <t>101 17</t>
+  </si>
+  <si>
+    <t>91 17</t>
+  </si>
+  <si>
+    <t>92 122</t>
+  </si>
+  <si>
+    <t>122 17</t>
+  </si>
+  <si>
+    <t>1224 1748</t>
+  </si>
+  <si>
+    <t>121 112</t>
+  </si>
+  <si>
+    <t>112 17</t>
+  </si>
+  <si>
+    <t>132 71</t>
+  </si>
+  <si>
+    <t>131 113</t>
+  </si>
+  <si>
+    <t>113 132</t>
+  </si>
+  <si>
+    <t>17 112</t>
+  </si>
+  <si>
+    <t>41 16</t>
+  </si>
+  <si>
+    <t>42 51</t>
+  </si>
+  <si>
+    <t>43 241</t>
+  </si>
+  <si>
+    <t>16 41</t>
+  </si>
+  <si>
+    <t>23 61</t>
+  </si>
+  <si>
+    <t>22 21</t>
+  </si>
+  <si>
+    <t>41 51</t>
   </si>
 </sst>
 </file>
@@ -847,11 +910,12 @@
     <col min="21" max="21" width="7" style="1" customWidth="1"/>
     <col min="22" max="22" width="6" style="1" customWidth="1"/>
     <col min="23" max="23" width="6.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" style="1" customWidth="1"/>
     <col min="25" max="25" width="6.5703125" style="1" customWidth="1"/>
     <col min="26" max="26" width="4.42578125" style="1" customWidth="1"/>
     <col min="27" max="27" width="6.28515625" style="1" customWidth="1"/>
-    <col min="28" max="29" width="5.140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="5.140625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="13.85546875" style="1" customWidth="1"/>
     <col min="30" max="30" width="5" style="1" customWidth="1"/>
     <col min="31" max="31" width="5.28515625" style="1" customWidth="1"/>
     <col min="32" max="33" width="5.140625" style="1" customWidth="1"/>
@@ -8614,17 +8678,19 @@
       <c r="P235" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="X235" s="1" t="s">
+      <c r="X235" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Y235" s="1" t="s">
+      <c r="Y235" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AA235" s="2" t="s">
         <v>96</v>
       </c>
       <c r="AB235" s="2"/>
-      <c r="AC235" s="2"/>
+      <c r="AC235" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="AD235" s="2"/>
       <c r="AE235" s="2"/>
       <c r="AF235" s="2"/>
@@ -8686,17 +8752,19 @@
     <row r="236" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
-      <c r="X236" s="1" t="s">
+      <c r="X236" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y236" s="1" t="s">
+      <c r="Y236" s="3" t="s">
         <v>9</v>
       </c>
       <c r="AA236" s="2" t="s">
         <v>106</v>
       </c>
       <c r="AB236" s="2"/>
-      <c r="AC236" s="2"/>
+      <c r="AC236" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="AD236" s="2"/>
       <c r="AE236" s="2"/>
       <c r="AF236" s="2"/>
@@ -8764,17 +8832,19 @@
       </c>
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
-      <c r="X237" s="1" t="s">
+      <c r="X237" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y237" s="1" t="s">
+      <c r="Y237" s="3" t="s">
         <v>43</v>
       </c>
       <c r="AA237" s="2" t="s">
         <v>110</v>
       </c>
       <c r="AB237" s="2"/>
-      <c r="AC237" s="2"/>
+      <c r="AC237" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="AD237" s="2"/>
       <c r="AE237" s="2"/>
       <c r="AF237" s="2"/>
@@ -8839,17 +8909,19 @@
     <row r="238" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
-      <c r="X238" s="1" t="s">
+      <c r="X238" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Y238" s="1" t="s">
+      <c r="Y238" s="3" t="s">
         <v>13</v>
       </c>
       <c r="AA238" s="2" t="s">
         <v>112</v>
       </c>
       <c r="AB238" s="2"/>
-      <c r="AC238" s="2"/>
+      <c r="AC238" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="AD238" s="2"/>
       <c r="AE238" s="2"/>
       <c r="AF238" s="2"/>
@@ -8937,17 +9009,19 @@
       <c r="V239" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="X239" s="1" t="s">
+      <c r="X239" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="Y239" s="1" t="s">
+      <c r="Y239" s="3" t="s">
         <v>18</v>
       </c>
       <c r="AA239" s="2" t="s">
         <v>115</v>
       </c>
       <c r="AB239" s="2"/>
-      <c r="AC239" s="2"/>
+      <c r="AC239" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="AD239" s="2"/>
       <c r="AE239" s="2"/>
       <c r="AF239" s="2"/>
@@ -9038,17 +9112,19 @@
       <c r="V240" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="X240" s="1" t="s">
+      <c r="X240" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="Y240" s="1" t="s">
+      <c r="Y240" s="3" t="s">
         <v>25</v>
       </c>
       <c r="AA240" s="2" t="s">
         <v>118</v>
       </c>
       <c r="AB240" s="2"/>
-      <c r="AC240" s="2"/>
+      <c r="AC240" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="AD240" s="2"/>
       <c r="AE240" s="2"/>
       <c r="AF240" s="2"/>
@@ -9139,17 +9215,19 @@
       <c r="V241" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="X241" s="1" t="s">
+      <c r="X241" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y241" s="1" t="s">
+      <c r="Y241" s="3" t="s">
         <v>0</v>
       </c>
       <c r="AA241" s="2" t="s">
         <v>119</v>
       </c>
       <c r="AB241" s="2"/>
-      <c r="AC241" s="2"/>
+      <c r="AC241" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="AD241" s="2"/>
       <c r="AE241" s="2"/>
       <c r="AF241" s="2"/>
@@ -9201,11 +9279,14 @@
       <c r="BW241" s="3"/>
     </row>
     <row r="242" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="X242" s="1" t="s">
+      <c r="X242" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Y242" s="1" t="s">
+      <c r="Y242" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="AC242" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="AW242" s="2"/>
       <c r="AX242" s="5" t="s">
@@ -9244,11 +9325,14 @@
       <c r="C243" t="s">
         <v>127</v>
       </c>
-      <c r="X243" s="1" t="s">
+      <c r="X243" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Y243" s="1" t="s">
+      <c r="Y243" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="AC243" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="AW243" s="2"/>
       <c r="AX243" s="5" t="s">
@@ -9287,11 +9371,14 @@
       <c r="C244" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="X244" s="1" t="s">
+      <c r="X244" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Y244" s="1" t="s">
+      <c r="Y244" s="3" t="s">
         <v>123</v>
+      </c>
+      <c r="AC244" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="AW244" s="2"/>
       <c r="AX244" s="2"/>
@@ -9324,11 +9411,14 @@
       <c r="C245" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X245" s="1" t="s">
+      <c r="X245" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Y245" s="1" t="s">
+      <c r="Y245" s="3" t="s">
         <v>124</v>
+      </c>
+      <c r="AC245" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="AW245" s="2"/>
       <c r="AX245" s="2"/>
@@ -9361,11 +9451,14 @@
       <c r="C246" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X246" s="1" t="s">
+      <c r="X246" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Y246" s="1" t="s">
+      <c r="Y246" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="AC246" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="AW246" s="2"/>
       <c r="AX246" s="2"/>
@@ -9392,11 +9485,14 @@
       <c r="BS246" s="2"/>
     </row>
     <row r="247" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="X247" s="1" t="s">
+      <c r="X247" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="Y247" s="1" t="s">
+      <c r="Y247" s="3" t="s">
         <v>125</v>
+      </c>
+      <c r="AC247" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="AW247" s="2"/>
       <c r="AX247" s="2"/>
@@ -9426,6 +9522,9 @@
       <c r="E248" s="1" t="s">
         <v>131</v>
       </c>
+      <c r="AC248" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="AW248" s="2"/>
       <c r="AX248" s="2"/>
       <c r="AY248" s="2"/>
@@ -9451,6 +9550,9 @@
       <c r="BS248" s="2"/>
     </row>
     <row r="249" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC249" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="AW249" s="2"/>
       <c r="AX249" s="2"/>
       <c r="AY249" s="2"/>
@@ -9476,6 +9578,9 @@
       <c r="BS249" s="2"/>
     </row>
     <row r="250" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC250" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="AW250" s="2"/>
       <c r="AX250" s="2"/>
       <c r="AY250" s="2"/>
@@ -9501,6 +9606,9 @@
       <c r="BS250" s="2"/>
     </row>
     <row r="251" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC251" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="AW251" s="2"/>
       <c r="AX251" s="2"/>
       <c r="AY251" s="2"/>
@@ -9526,6 +9634,9 @@
       <c r="BS251" s="2"/>
     </row>
     <row r="252" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC252" s="12" t="s">
+        <v>149</v>
+      </c>
       <c r="AW252" s="5"/>
       <c r="AX252" s="5"/>
       <c r="AY252" s="5"/>
@@ -9551,6 +9662,9 @@
       <c r="BS252" s="5"/>
     </row>
     <row r="253" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC253" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="AW253" s="5"/>
       <c r="AX253" s="5"/>
       <c r="AY253" s="5"/>
@@ -9576,6 +9690,9 @@
       <c r="BS253" s="5"/>
     </row>
     <row r="254" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC254" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="AW254" s="5"/>
       <c r="AX254" s="5"/>
       <c r="AY254" s="5"/>
@@ -9601,6 +9718,9 @@
       <c r="BS254" s="5"/>
     </row>
     <row r="255" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AC255" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="AW255" s="5"/>
       <c r="AX255" s="5"/>
       <c r="AY255" s="5"/>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="146">
   <si>
     <t>2.1</t>
   </si>
@@ -421,39 +421,21 @@
     <t>82 101</t>
   </si>
   <si>
-    <t>101 17</t>
-  </si>
-  <si>
-    <t>91 17</t>
-  </si>
-  <si>
     <t>92 122</t>
   </si>
   <si>
-    <t>122 17</t>
-  </si>
-  <si>
     <t>1224 1748</t>
   </si>
   <si>
     <t>121 112</t>
   </si>
   <si>
-    <t>112 17</t>
-  </si>
-  <si>
     <t>132 71</t>
   </si>
   <si>
     <t>131 113</t>
   </si>
   <si>
-    <t>113 132</t>
-  </si>
-  <si>
-    <t>17 112</t>
-  </si>
-  <si>
     <t>41 16</t>
   </si>
   <si>
@@ -463,16 +445,13 @@
     <t>43 241</t>
   </si>
   <si>
-    <t>16 41</t>
-  </si>
-  <si>
     <t>23 61</t>
   </si>
   <si>
     <t>22 21</t>
   </si>
   <si>
-    <t>41 51</t>
+    <t>Programm</t>
   </si>
 </sst>
 </file>
@@ -8606,7 +8585,9 @@
         <v>95</v>
       </c>
       <c r="AB234" s="2"/>
-      <c r="AC234" s="2"/>
+      <c r="AC234" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="AD234" s="2"/>
       <c r="AE234" s="2"/>
       <c r="AF234" s="2"/>
@@ -8919,9 +8900,7 @@
         <v>112</v>
       </c>
       <c r="AB238" s="2"/>
-      <c r="AC238" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="AC238" s="2"/>
       <c r="AD238" s="2"/>
       <c r="AE238" s="2"/>
       <c r="AF238" s="2"/>
@@ -9019,9 +8998,7 @@
         <v>115</v>
       </c>
       <c r="AB239" s="2"/>
-      <c r="AC239" s="2" t="s">
-        <v>136</v>
-      </c>
+      <c r="AC239" s="2"/>
       <c r="AD239" s="2"/>
       <c r="AE239" s="2"/>
       <c r="AF239" s="2"/>
@@ -9123,7 +9100,7 @@
       </c>
       <c r="AB240" s="2"/>
       <c r="AC240" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AD240" s="2"/>
       <c r="AE240" s="2"/>
@@ -9225,9 +9202,7 @@
         <v>119</v>
       </c>
       <c r="AB241" s="2"/>
-      <c r="AC241" s="2" t="s">
-        <v>138</v>
-      </c>
+      <c r="AC241" s="2"/>
       <c r="AD241" s="2"/>
       <c r="AE241" s="2"/>
       <c r="AF241" s="2"/>
@@ -9286,7 +9261,7 @@
         <v>42</v>
       </c>
       <c r="AC242" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AW242" s="2"/>
       <c r="AX242" s="5" t="s">
@@ -9332,7 +9307,7 @@
         <v>21</v>
       </c>
       <c r="AC243" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AW243" s="2"/>
       <c r="AX243" s="5" t="s">
@@ -9376,9 +9351,6 @@
       </c>
       <c r="Y244" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="AC244" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="AW244" s="2"/>
       <c r="AX244" s="2"/>
@@ -9418,7 +9390,7 @@
         <v>124</v>
       </c>
       <c r="AC245" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AW245" s="2"/>
       <c r="AX245" s="2"/>
@@ -9458,7 +9430,7 @@
         <v>20</v>
       </c>
       <c r="AC246" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AW246" s="2"/>
       <c r="AX246" s="2"/>
@@ -9491,9 +9463,6 @@
       <c r="Y247" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AC247" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="AW247" s="2"/>
       <c r="AX247" s="2"/>
       <c r="AY247" s="2"/>
@@ -9522,9 +9491,6 @@
       <c r="E248" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AC248" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="AW248" s="2"/>
       <c r="AX248" s="2"/>
       <c r="AY248" s="2"/>
@@ -9551,7 +9517,7 @@
     </row>
     <row r="249" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AC249" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AW249" s="2"/>
       <c r="AX249" s="2"/>
@@ -9579,7 +9545,7 @@
     </row>
     <row r="250" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AC250" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AW250" s="2"/>
       <c r="AX250" s="2"/>
@@ -9607,7 +9573,7 @@
     </row>
     <row r="251" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AC251" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="AW251" s="2"/>
       <c r="AX251" s="2"/>
@@ -9634,9 +9600,7 @@
       <c r="BS251" s="2"/>
     </row>
     <row r="252" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="AC252" s="12" t="s">
-        <v>149</v>
-      </c>
+      <c r="AC252" s="12"/>
       <c r="AW252" s="5"/>
       <c r="AX252" s="5"/>
       <c r="AY252" s="5"/>
@@ -9663,7 +9627,7 @@
     </row>
     <row r="253" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AC253" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AW253" s="5"/>
       <c r="AX253" s="5"/>
@@ -9691,7 +9655,7 @@
     </row>
     <row r="254" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AC254" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AW254" s="5"/>
       <c r="AX254" s="5"/>
@@ -9718,9 +9682,6 @@
       <c r="BS254" s="5"/>
     </row>
     <row r="255" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="AC255" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="AW255" s="5"/>
       <c r="AX255" s="5"/>
       <c r="AY255" s="5"/>
